--- a/Results/Two_Datasets_Assessment/Mushroom/Processed_Data/privacy_scores.xlsx
+++ b/Results/Two_Datasets_Assessment/Mushroom/Processed_Data/privacy_scores.xlsx
@@ -475,13 +475,13 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>0.5965175288041394</v>
+        <v>0.5651465293055633</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2422318876841711</v>
+        <v>0.3057528156749705</v>
       </c>
       <c r="F2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3">
@@ -499,13 +499,13 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>0.5898036904498916</v>
+        <v>0.6793990320601035</v>
       </c>
       <c r="E3" t="n">
-        <v>0.3382438588682164</v>
+        <v>0.3920273153705516</v>
       </c>
       <c r="F3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4">
@@ -523,13 +523,13 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>0.425874725649952</v>
+        <v>0.580711160887031</v>
       </c>
       <c r="E4" t="n">
-        <v>0.4421103533686161</v>
+        <v>0.4742130076258645</v>
       </c>
       <c r="F4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5">
@@ -547,13 +547,13 @@
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>0.8740643163992137</v>
+        <v>0.6501790175485291</v>
       </c>
       <c r="E5" t="n">
-        <v>0.2181270024824805</v>
+        <v>0.3697767981582697</v>
       </c>
       <c r="F5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6">
@@ -571,13 +571,13 @@
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>0.4949530413496791</v>
+        <v>0.542977064252405</v>
       </c>
       <c r="E6" t="n">
-        <v>0.414551150728962</v>
+        <v>0.4540085148638113</v>
       </c>
       <c r="F6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7">
@@ -595,13 +595,13 @@
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>0.6238393249874938</v>
+        <v>0.7325289107288828</v>
       </c>
       <c r="E7" t="n">
-        <v>0.3788110168065982</v>
+        <v>0.3846235259007812</v>
       </c>
       <c r="F7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8">
@@ -619,13 +619,13 @@
         <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>0.25</v>
+        <v>0.2294567983077689</v>
       </c>
       <c r="E8" t="n">
-        <v>0.4330127018922193</v>
+        <v>0.37104157201863</v>
       </c>
       <c r="F8" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9">
@@ -643,13 +643,13 @@
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>0.5520664642022749</v>
+        <v>0.5187481196936311</v>
       </c>
       <c r="E9" t="n">
-        <v>0.2518670578036035</v>
+        <v>0.3424820228872009</v>
       </c>
       <c r="F9" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
